--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mood/current_mood_vs_checkout_style.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mood/current_mood_vs_checkout_style.xlsx
@@ -473,13 +473,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -545,7 +545,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
         <v>11</v>
       </c>
-      <c r="D6" t="n">
-        <v>9</v>
-      </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -583,13 +583,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -627,13 +627,13 @@
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
